--- a/registro truco.xlsx
+++ b/registro truco.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Debe</t>
   </si>
@@ -57,6 +57,9 @@
   </si>
   <si>
     <t>disney</t>
+  </si>
+  <si>
+    <t>flor me debe</t>
   </si>
 </sst>
 </file>
@@ -422,7 +425,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -440,6 +443,46 @@
       <top style="thin">
         <color auto="1"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -449,9 +492,44 @@
       <left style="thin">
         <color auto="1"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -578,7 +656,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -590,34 +668,34 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="14" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="15" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -702,7 +780,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -715,13 +793,52 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -1265,9 +1382,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:L27"/>
+  <dimension ref="A2:L45"/>
   <sheetFormatPr defaultColWidth="9.14285714285714" defaultRowHeight="15"/>
   <cols>
+    <col min="3" max="3" width="12.7142857142857" customWidth="1"/>
     <col min="4" max="4" width="18.2857142857143" customWidth="1"/>
     <col min="5" max="5" width="16.8571428571429" customWidth="1"/>
   </cols>
@@ -1299,7 +1417,7 @@
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="20" t="s">
         <v>2</v>
       </c>
       <c r="J3" s="1"/>
@@ -1312,7 +1430,7 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
-      <c r="D4" s="2">
+      <c r="D4" s="4">
         <v>1500</v>
       </c>
       <c r="E4" s="2"/>
@@ -1320,8 +1438,8 @@
       <c r="G4" s="1"/>
       <c r="H4" s="1"/>
       <c r="I4" s="1">
-        <f>D25-E25</f>
-        <v>44530</v>
+        <f>D45-E45</f>
+        <v>53409</v>
       </c>
       <c r="J4" s="1"/>
       <c r="K4" s="1"/>
@@ -1331,8 +1449,8 @@
       <c r="A5" s="1"/>
       <c r="B5" s="1"/>
       <c r="C5" s="1"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D5" s="5"/>
+      <c r="E5" s="6"/>
       <c r="F5" s="1"/>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -1347,10 +1465,10 @@
       </c>
       <c r="B6" s="1"/>
       <c r="C6" s="1"/>
-      <c r="D6" s="2">
+      <c r="D6" s="5">
         <v>1600</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="6"/>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
       <c r="H6" s="1" t="s">
@@ -1367,20 +1485,20 @@
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2">
+      <c r="D7" s="7"/>
+      <c r="E7" s="8">
         <v>1000</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
-      <c r="H7" s="4">
+      <c r="H7" s="9">
         <f>SUM(D3:D24)</f>
-        <v>66230</v>
+        <v>98634</v>
       </c>
       <c r="I7" s="1"/>
-      <c r="J7" s="4">
-        <f>SUM(E24:E25)</f>
-        <v>21700</v>
+      <c r="J7" s="9">
+        <f>SUM(E24:E45)</f>
+        <v>59670</v>
       </c>
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
@@ -1389,8 +1507,8 @@
       <c r="A8" s="1"/>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="2"/>
+      <c r="D8" s="5"/>
+      <c r="E8" s="6"/>
       <c r="F8" s="1"/>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -1405,10 +1523,10 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-      <c r="D9" s="2">
+      <c r="D9" s="5">
         <v>5800</v>
       </c>
-      <c r="E9" s="2">
+      <c r="E9" s="6">
         <v>1000</v>
       </c>
       <c r="F9" s="1"/>
@@ -1423,10 +1541,10 @@
       <c r="A10" s="1"/>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
-      <c r="D10" s="2">
+      <c r="D10" s="5">
         <v>1830</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="6"/>
       <c r="F10" s="1"/>
       <c r="G10" s="1"/>
       <c r="H10" s="1"/>
@@ -1441,10 +1559,10 @@
         <v>7</v>
       </c>
       <c r="C11" s="1"/>
-      <c r="D11" s="2">
+      <c r="D11" s="5">
         <v>50000</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="6"/>
       <c r="F11" s="1"/>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
@@ -1457,8 +1575,8 @@
       <c r="A12" s="1"/>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
+      <c r="D12" s="5"/>
+      <c r="E12" s="6"/>
       <c r="F12" s="1"/>
       <c r="G12" s="1"/>
       <c r="H12" s="1"/>
@@ -1471,8 +1589,8 @@
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="2"/>
-      <c r="E13" s="2"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="8"/>
       <c r="F13" s="1"/>
       <c r="G13" s="1"/>
       <c r="H13" s="1"/>
@@ -1487,8 +1605,8 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2">
+      <c r="D14" s="5"/>
+      <c r="E14" s="6">
         <v>1000</v>
       </c>
       <c r="F14" s="1"/>
@@ -1503,10 +1621,12 @@
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
-      <c r="D15" s="2">
+      <c r="D15" s="5">
         <v>5500</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="6">
+        <v>1000</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
       <c r="H15" s="1"/>
@@ -1521,13 +1641,15 @@
       <c r="C16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2">
+      <c r="D16" s="5"/>
+      <c r="E16" s="6">
         <v>18400</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
+      <c r="H16" s="1">
+        <v>2300</v>
+      </c>
       <c r="I16" s="1"/>
       <c r="J16" s="1"/>
       <c r="K16" s="1"/>
@@ -1536,9 +1658,11 @@
     <row r="17" spans="1:12">
       <c r="A17" s="1"/>
       <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2">
+      <c r="C17" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D17" s="5"/>
+      <c r="E17" s="6">
         <v>300</v>
       </c>
       <c r="F17" s="1"/>
@@ -1553,8 +1677,12 @@
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
+      <c r="D18" s="5">
+        <v>13000</v>
+      </c>
+      <c r="E18" s="6">
+        <v>11534</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
       <c r="H18" s="1"/>
@@ -1567,8 +1695,12 @@
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
+      <c r="D19" s="5">
+        <v>3400</v>
+      </c>
+      <c r="E19" s="6">
+        <v>7100</v>
+      </c>
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -1581,22 +1713,32 @@
       <c r="A20" s="1"/>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
+      <c r="D20" s="5">
+        <v>204</v>
+      </c>
+      <c r="E20" s="6"/>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+      <c r="J20" s="1">
+        <f>D4+D6+D9+D15+D18+D19+D21+D22+D23+D24+D25</f>
+        <v>49200</v>
+      </c>
+      <c r="K20" s="1">
+        <f>E14+E15+E7+E9+D27+E24</f>
+        <v>15696</v>
+      </c>
       <c r="L20" s="1"/>
     </row>
     <row r="21" spans="1:12">
       <c r="A21" s="1"/>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
+      <c r="D21" s="5">
+        <v>5500</v>
+      </c>
+      <c r="E21" s="6"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1"/>
@@ -1609,8 +1751,10 @@
       <c r="A22" s="1"/>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
-      <c r="D22" s="2"/>
-      <c r="E22" s="2"/>
+      <c r="D22" s="5">
+        <v>2500</v>
+      </c>
+      <c r="E22" s="6"/>
       <c r="F22" s="1"/>
       <c r="G22" s="1"/>
       <c r="H22" s="1"/>
@@ -1623,13 +1767,18 @@
       <c r="A23" s="1"/>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
-      <c r="D23" s="2"/>
-      <c r="E23" s="2"/>
+      <c r="D23" s="5">
+        <v>1400</v>
+      </c>
+      <c r="E23" s="6"/>
       <c r="F23" s="1"/>
       <c r="G23" s="1"/>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
+      <c r="J23" s="1">
+        <f>J20-K20</f>
+        <v>33504</v>
+      </c>
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
     </row>
@@ -1637,8 +1786,12 @@
       <c r="A24" s="1"/>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
-      <c r="D24" s="2"/>
-      <c r="E24" s="2"/>
+      <c r="D24" s="7">
+        <v>6400</v>
+      </c>
+      <c r="E24" s="8">
+        <v>9096</v>
+      </c>
       <c r="F24" s="1"/>
       <c r="G24" s="1"/>
       <c r="H24" s="1"/>
@@ -1651,13 +1804,11 @@
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="5">
-        <f>SUM(D3:D24)</f>
-        <v>66230</v>
-      </c>
-      <c r="E25" s="6">
-        <f>SUM(E3:E24)</f>
-        <v>21700</v>
+      <c r="D25" s="10">
+        <v>2600</v>
+      </c>
+      <c r="E25" s="11">
+        <v>72</v>
       </c>
       <c r="F25" s="1"/>
       <c r="G25" s="1"/>
@@ -1671,8 +1822,10 @@
       <c r="A26" s="1"/>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
+      <c r="D26" s="12">
+        <v>77</v>
+      </c>
+      <c r="E26" s="13"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
@@ -1685,8 +1838,10 @@
       <c r="A27" s="1"/>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
+      <c r="D27" s="12">
+        <v>2600</v>
+      </c>
+      <c r="E27" s="13"/>
       <c r="F27" s="1"/>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
@@ -1695,6 +1850,84 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
     </row>
+    <row r="28" spans="4:5">
+      <c r="D28" s="14"/>
+      <c r="E28" s="15"/>
+    </row>
+    <row r="29" spans="4:5">
+      <c r="D29" s="14"/>
+      <c r="E29" s="15"/>
+    </row>
+    <row r="30" spans="4:5">
+      <c r="D30" s="14"/>
+      <c r="E30" s="15"/>
+    </row>
+    <row r="31" spans="4:5">
+      <c r="D31" s="14"/>
+      <c r="E31" s="15"/>
+    </row>
+    <row r="32" spans="4:5">
+      <c r="D32" s="14"/>
+      <c r="E32" s="15"/>
+    </row>
+    <row r="33" spans="4:5">
+      <c r="D33" s="14"/>
+      <c r="E33" s="15"/>
+    </row>
+    <row r="34" spans="4:5">
+      <c r="D34" s="14"/>
+      <c r="E34" s="15"/>
+    </row>
+    <row r="35" spans="4:5">
+      <c r="D35" s="14"/>
+      <c r="E35" s="15"/>
+    </row>
+    <row r="36" spans="4:5">
+      <c r="D36" s="14"/>
+      <c r="E36" s="15"/>
+    </row>
+    <row r="37" spans="4:5">
+      <c r="D37" s="14"/>
+      <c r="E37" s="15"/>
+    </row>
+    <row r="38" spans="4:5">
+      <c r="D38" s="14"/>
+      <c r="E38" s="15"/>
+    </row>
+    <row r="39" spans="4:5">
+      <c r="D39" s="14"/>
+      <c r="E39" s="15"/>
+    </row>
+    <row r="40" spans="4:5">
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+    </row>
+    <row r="41" spans="4:5">
+      <c r="D41" s="14"/>
+      <c r="E41" s="15"/>
+    </row>
+    <row r="42" spans="4:5">
+      <c r="D42" s="14"/>
+      <c r="E42" s="15"/>
+    </row>
+    <row r="43" spans="4:5">
+      <c r="D43" s="14"/>
+      <c r="E43" s="15"/>
+    </row>
+    <row r="44" spans="4:5">
+      <c r="D44" s="16"/>
+      <c r="E44" s="17"/>
+    </row>
+    <row r="45" spans="4:5">
+      <c r="D45" s="18">
+        <f>SUM(D4:D44)</f>
+        <v>103911</v>
+      </c>
+      <c r="E45" s="19">
+        <f>SUM(E4:E44)</f>
+        <v>50502</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
